--- a/data/trans_camb/IP16B01-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16B01-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>81,97; 100,0</t>
+          <t>80,03; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50,07; 90,25</t>
+          <t>48,58; 92,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75,11; 96,78</t>
+          <t>75,23; 96,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46,92; 93,31</t>
+          <t>44,77; 92,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>82,73; 97,07</t>
+          <t>83,7; 97,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,15; 88,52</t>
+          <t>58,59; 89,51</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51,08; 83,17</t>
+          <t>54,0; 83,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>76,25; 97,16</t>
+          <t>76,3; 97,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86,78; 100,0</t>
+          <t>85,72; 100,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>78,35; 97,6</t>
+          <t>79,94; 97,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>72,31; 91,1</t>
+          <t>73,0; 91,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>82,81; 95,3</t>
+          <t>82,74; 95,33</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>56,41; 85,56</t>
+          <t>57,64; 87,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>59,47; 90,1</t>
+          <t>56,2; 89,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85,04; 100,0</t>
+          <t>85,1; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76,51; 100,0</t>
+          <t>75,28; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>75,15; 92,33</t>
+          <t>75,36; 92,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,62; 92,35</t>
+          <t>72,3; 92,56</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>71,19; 94,75</t>
+          <t>70,52; 94,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>55,47; 89,12</t>
+          <t>56,02; 88,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77,55; 97,76</t>
+          <t>79,05; 97,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67,57; 96,22</t>
+          <t>67,31; 96,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>79,67; 94,56</t>
+          <t>78,49; 94,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,61; 89,82</t>
+          <t>68,99; 90,8</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>74,24; 86,95</t>
+          <t>74,06; 87,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>72,36; 87,82</t>
+          <t>72,17; 87,06</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>87,87; 96,99</t>
+          <t>88,05; 97,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>81,16; 93,98</t>
+          <t>80,09; 93,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>83,27; 90,84</t>
+          <t>83,07; 90,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>79,33; 89,01</t>
+          <t>78,98; 88,59</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2147,22; —</t>
+          <t>2177,73; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2188,07; —</t>
+          <t>2006,35; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5034,97; —</t>
+          <t>5681,2; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4693,67; —</t>
+          <t>5285,63; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B01-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16B01-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>80,03; 100,0</t>
+          <t>81,19; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>48,58; 92,05</t>
+          <t>51,82; 91,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75,23; 96,72</t>
+          <t>72,9; 96,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44,77; 92,95</t>
+          <t>49,19; 93,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>83,7; 97,25</t>
+          <t>83,28; 98,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,59; 89,51</t>
+          <t>57,09; 88,8</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54,0; 83,29</t>
+          <t>54,18; 84,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>76,3; 97,12</t>
+          <t>76,61; 97,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85,72; 100,0</t>
+          <t>86,86; 100,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>79,94; 97,59</t>
+          <t>79,05; 97,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>73,0; 91,16</t>
+          <t>73,19; 90,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>82,74; 95,33</t>
+          <t>81,71; 95,41</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>57,64; 87,49</t>
+          <t>57,12; 87,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>56,2; 89,67</t>
+          <t>57,73; 89,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85,1; 100,0</t>
+          <t>85,04; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75,28; 100,0</t>
+          <t>71,54; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>75,36; 92,5</t>
+          <t>75,04; 92,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,3; 92,56</t>
+          <t>72,43; 92,17</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>70,52; 94,49</t>
+          <t>69,53; 94,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>56,02; 88,86</t>
+          <t>57,87; 91,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79,05; 97,76</t>
+          <t>78,34; 97,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67,31; 96,22</t>
+          <t>65,94; 96,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>78,49; 94,29</t>
+          <t>79,75; 94,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,99; 90,8</t>
+          <t>67,45; 91,18</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>74,06; 87,17</t>
+          <t>73,61; 87,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>72,17; 87,06</t>
+          <t>72,02; 86,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>88,05; 97,03</t>
+          <t>87,96; 96,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>80,09; 93,75</t>
+          <t>80,18; 93,61</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>83,07; 90,83</t>
+          <t>83,1; 90,82</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>78,98; 88,59</t>
+          <t>78,97; 88,82</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2177,73; —</t>
+          <t>2357,06; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2006,35; —</t>
+          <t>2324,28; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5681,2; —</t>
+          <t>4396,5; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5285,63; —</t>
+          <t>4694,45; —</t>
         </is>
       </c>
     </row>
